--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_194_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_194_R20.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1632</v>
+        <v>5.364</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7034</v>
+        <v>4.2066</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4598</v>
+        <v>1.1574</v>
       </c>
       <c r="G2" t="n">
         <v>7.1771</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.1327</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4753</v>
+        <v>0.0279</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4072</v>
+        <v>0.1048</v>
       </c>
       <c r="V2" t="n">
         <v>0.1418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4042</v>
+        <v>3.6122</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2424</v>
+        <v>2.4167</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1618</v>
+        <v>1.1954</v>
       </c>
       <c r="G3" t="n">
         <v>4.683</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5046</v>
+        <v>0.7125</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9347</v>
+        <v>1.109</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4301</v>
+        <v>-0.3965</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7659</v>
+        <v>2.9813</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7186</v>
+        <v>1.9676</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0473</v>
+        <v>1.0137</v>
       </c>
       <c r="G4" t="n">
         <v>3.9353</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8332</v>
+        <v>1.0486</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9347</v>
+        <v>1.1837</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1015</v>
+        <v>-0.1351</v>
       </c>
       <c r="V4" t="n">
         <v>-2.0026</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1742</v>
+        <v>2.4415</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0692</v>
+        <v>3.3365</v>
       </c>
       <c r="F5" t="n">
         <v>-0.895</v>
@@ -844,10 +844,10 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5544</v>
+        <v>0.8217</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1221</v>
+        <v>0.3894</v>
       </c>
       <c r="U5" t="n">
         <v>0.4323</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8492</v>
+        <v>1.2703</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8195</v>
+        <v>1.1734</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0297</v>
+        <v>0.0969</v>
       </c>
       <c r="G6" t="n">
         <v>0.5573</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1204</v>
+        <v>0.3007</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0905</v>
+        <v>0.4443</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2109</v>
+        <v>-0.1436</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2836</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5138</v>
+        <v>0.3958</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7552</v>
+        <v>1.6373</v>
       </c>
       <c r="F7" t="n">
         <v>-1.2415</v>
@@ -1000,10 +1000,10 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2987</v>
+        <v>0.1808</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6528</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U7" t="n">
         <v>-0.3541</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6152</v>
+        <v>-0.6234</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4293</v>
+        <v>-0.9848</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8141</v>
+        <v>0.3614</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5534</v>
+        <v>-1.164</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0742</v>
+        <v>-1.378</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4791</v>
+        <v>0.214</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5029</v>
+        <v>-0.6665</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7661</v>
+        <v>-0.1478</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.7369</v>
+        <v>-0.5188</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0504</v>
+        <v>-0.4974</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3082</v>
+        <v>-1.2303</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2578</v>
+        <v>0.7328</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7784</v>
+        <v>-0.1553</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0736</v>
+        <v>-0.3183</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2952</v>
+        <v>0.163</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0594</v>
+        <v>-0.8943</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.488</v>
+        <v>-1.7085</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4286</v>
+        <v>0.8141</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.164</v>
+        <v>-2.5534</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.378</v>
+        <v>-1.0742</v>
       </c>
       <c r="I9" t="n">
-        <v>0.214</v>
+        <v>-1.4791</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6665</v>
+        <v>-2.5029</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1478</v>
+        <v>-0.7661</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5188</v>
+        <v>-1.7369</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4974</v>
+        <v>-0.0504</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2303</v>
+        <v>-0.3082</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7328</v>
+        <v>0.2578</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5913</v>
+        <v>0.4993</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8215</v>
+        <v>0.7945</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2302</v>
+        <v>-0.2952</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1444</v>
+        <v>-1.7569</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2589</v>
+        <v>0.0949</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8855</v>
+        <v>-1.8519</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2519</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7481</v>
+        <v>-0.3607</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>-0.3183</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2439</v>
+        <v>-3.236</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0693</v>
+        <v>-2.3302</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1746</v>
+        <v>-0.9058</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0681</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4954</v>
+        <v>-0.4874</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0455</v>
+        <v>-0.3064</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4498</v>
+        <v>-0.181</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.807599999999997</v>
+        <v>9.554500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>9.062799999999998</v>
+        <v>9.809500000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2552999999999999</v>
+        <v>-0.2553</v>
       </c>
       <c r="G12" t="n">
         <v>13.2945</v>
@@ -1390,13 +1390,13 @@
         <v>9.278299999999998</v>
       </c>
       <c r="S12" t="n">
-        <v>1.946</v>
+        <v>2.6929</v>
       </c>
       <c r="T12" t="n">
-        <v>2.794</v>
+        <v>3.5406</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8479000000000001</v>
+        <v>-0.8478000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-6.433199999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7278</v>
+        <v>4.762</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7419</v>
+        <v>6.506</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0141</v>
+        <v>-1.744</v>
       </c>
       <c r="G13" t="n">
         <v>0.8108</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0677</v>
+        <v>-0.0334</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3857</v>
+        <v>0.1498</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4533</v>
+        <v>-0.1832</v>
       </c>
       <c r="V13" t="n">
         <v>3.7527</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3049</v>
+        <v>1.5376</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5586</v>
+        <v>2.0252</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2536</v>
+        <v>-0.4876</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6465</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9025</v>
+        <v>1.1352</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3318</v>
+        <v>0.7984</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5707</v>
+        <v>0.3367</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1107</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6584</v>
+        <v>0.7991</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5799</v>
+        <v>0.7543</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0784</v>
+        <v>0.0448</v>
       </c>
       <c r="G15" t="n">
         <v>0.4201</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5424</v>
+        <v>0.6831</v>
       </c>
       <c r="T15" t="n">
-        <v>1.274</v>
+        <v>0.4483</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2684</v>
+        <v>0.2348</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0881</v>
+        <v>0.61</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0709</v>
+        <v>0.2829</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1591</v>
+        <v>0.3271</v>
       </c>
       <c r="G16" t="n">
         <v>0.5739</v>
@@ -1702,13 +1702,13 @@
         <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5759</v>
+        <v>-0.054</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3734</v>
+        <v>-0.0196</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3802</v>
+        <v>-0.4276</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4297</v>
+        <v>1.0683</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0495</v>
+        <v>-1.4958</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.0497</v>
+        <v>-3.0147</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0191</v>
+        <v>-1.6662</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0305</v>
+        <v>-1.3485</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.4668</v>
+        <v>-0.8945</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9677</v>
+        <v>0.4474</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4991</v>
+        <v>-1.3419</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5829</v>
+        <v>-2.1202</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0514</v>
+        <v>-2.1136</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4685</v>
+        <v>-0.0065</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4929</v>
+        <v>-0.0934</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0351</v>
+        <v>-0.094</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4577</v>
+        <v>0.0007</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4665</v>
+        <v>2.6805</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>3.2166</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7422</v>
+        <v>-1.0844</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1247</v>
+        <v>-0.5462</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8668</v>
+        <v>-0.5382</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0147</v>
+        <v>-1.4115</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6662</v>
+        <v>-1.1069</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3485</v>
+        <v>-0.3046</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8945</v>
+        <v>-0.0462</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4474</v>
+        <v>0.1449</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3419</v>
+        <v>-0.1911</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1202</v>
+        <v>-1.3654</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1136</v>
+        <v>-1.2518</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0065</v>
+        <v>-0.1136</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1858,28 +1858,28 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.408</v>
+        <v>-0.7451</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0376</v>
+        <v>-0.4125</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3703</v>
+        <v>-0.3325</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>3.2166</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2854</v>
+        <v>-1.2293</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2539</v>
+        <v>-1.5477</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0315</v>
+        <v>0.3184</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4115</v>
+        <v>-3.0497</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1069</v>
+        <v>-2.0191</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3046</v>
+        <v>-1.0305</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0462</v>
+        <v>-2.4668</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1449</v>
+        <v>-0.9677</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1911</v>
+        <v>-1.4991</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3654</v>
+        <v>-0.5829</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2518</v>
+        <v>-1.0514</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1136</v>
+        <v>0.4685</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9461</v>
+        <v>-0.342</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1202</v>
+        <v>-0.1531</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8259</v>
+        <v>-0.1889</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0722</v>
+        <v>1.4665</v>
       </c>
       <c r="W19" t="n">
         <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6302</v>
+        <v>-2.2148</v>
       </c>
       <c r="E20" t="n">
         <v>-0.5597</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0705</v>
+        <v>-1.6552</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9476</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3062</v>
+        <v>0.1092</v>
       </c>
       <c r="T20" t="n">
         <v>0.1968</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.503</v>
+        <v>-0.0876</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8924</v>
+        <v>-3.2469</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4067</v>
+        <v>-2.0528</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4857</v>
+        <v>-1.1941</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2112</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0034</v>
+        <v>-0.3578</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6721</v>
+        <v>-0.3183</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3312</v>
+        <v>-0.0395</v>
       </c>
       <c r="V21" t="n">
         <v>-1.214</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6564</v>
+        <v>-5.9544</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.4929</v>
+        <v>-5.1391</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1635</v>
+        <v>-0.8153</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8182</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5909</v>
+        <v>0.1111</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1019</v>
+        <v>0.2519</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4889</v>
+        <v>-0.1408</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.807600000000001</v>
+        <v>-6.448699999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7912999999999997</v>
+        <v>0.7912000000000008</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.598700000000001</v>
+        <v>-7.239899999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-13.2946</v>
@@ -2218,7 +2218,7 @@
         <v>-6.452500000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.8422</v>
+        <v>-6.842199999999999</v>
       </c>
       <c r="J23" t="n">
         <v>0.2185000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>9.2784</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9462</v>
+        <v>0.4128999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8479999999999999</v>
+        <v>0.8477</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.7937</v>
+        <v>-0.4348000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>6.433199999999999</v>
